--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -480,7 +480,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -660,6 +660,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -669,7 +672,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -848,6 +851,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -891,7 +897,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1071,6 +1077,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1080,7 +1089,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1260,6 +1269,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2263014.35528298</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2307327.5016448041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1302,7 +1314,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1482,6 +1494,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1491,7 +1506,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1671,6 +1686,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>913646.19172686804</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>957959.33808869217</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1692,11 +1710,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401691008"/>
-        <c:axId val="401692928"/>
+        <c:axId val="437855360"/>
+        <c:axId val="437856896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401691008"/>
+        <c:axId val="437855360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1739,14 +1757,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401692928"/>
+        <c:crossAx val="437856896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401692928"/>
+        <c:axId val="437856896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1797,7 +1815,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401691008"/>
+        <c:crossAx val="437855360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1988,7 +2006,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2168,6 +2186,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-72114.733350567156</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-120278.52715325328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2182,8 +2203,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="401885056"/>
-        <c:axId val="401883136"/>
+        <c:axId val="437879168"/>
+        <c:axId val="437872896"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2208,7 +2229,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2388,6 +2409,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2397,7 +2421,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2577,6 +2601,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2593,11 +2620,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401722752"/>
-        <c:axId val="401724928"/>
+        <c:axId val="437868416"/>
+        <c:axId val="437870976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401722752"/>
+        <c:axId val="437868416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2640,14 +2667,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401724928"/>
+        <c:crossAx val="437870976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401724928"/>
+        <c:axId val="437870976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2698,12 +2725,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401722752"/>
+        <c:crossAx val="437868416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="401883136"/>
+        <c:axId val="437872896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2740,12 +2767,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401885056"/>
+        <c:crossAx val="437879168"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="401885056"/>
+        <c:axId val="437879168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2754,7 +2781,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="401883136"/>
+        <c:crossAx val="437872896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3163,7 +3190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5967,6 +5994,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:13" ht="12.75">
+      <c r="A63" s="11">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="12">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="12">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="13">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="13">
+        <v>-120278.52715325328</v>
+      </c>
+      <c r="F63" s="14">
+        <v>-94262.166924579549</v>
+      </c>
+      <c r="G63" s="14">
+        <v>1335193.3317966722</v>
+      </c>
+      <c r="H63" s="14">
+        <v>1703706.7219327039</v>
+      </c>
+      <c r="I63" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J63" s="14">
+        <v>2307327.5016448041</v>
+      </c>
+      <c r="K63" s="14">
+        <v>957959.33808869217</v>
+      </c>
+      <c r="L63" s="13">
+        <v>603620.77971210016</v>
+      </c>
+      <c r="M63" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,10 +75,6 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -480,7 +476,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -663,6 +659,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -672,7 +671,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -854,6 +853,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -897,7 +899,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1080,6 +1082,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1089,7 +1094,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1272,6 +1277,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2307327.5016448041</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2081679.7890976393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1314,7 +1322,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1497,6 +1505,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1506,7 +1517,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1689,6 +1700,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>957959.33808869217</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>732311.62554152729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1710,11 +1724,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437855360"/>
-        <c:axId val="437856896"/>
+        <c:axId val="92879104"/>
+        <c:axId val="92880896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437855360"/>
+        <c:axId val="92879104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1757,14 +1771,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437856896"/>
+        <c:crossAx val="92880896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="437856896"/>
+        <c:axId val="92880896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1815,7 +1829,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437855360"/>
+        <c:crossAx val="92879104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2006,7 +2020,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2189,6 +2203,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-120278.52715325328</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-70500.180121343234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2203,8 +2220,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="437879168"/>
-        <c:axId val="437872896"/>
+        <c:axId val="92908160"/>
+        <c:axId val="92906240"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2229,7 +2246,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2412,6 +2429,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2421,7 +2441,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2604,6 +2624,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2620,11 +2643,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437868416"/>
-        <c:axId val="437870976"/>
+        <c:axId val="92898432"/>
+        <c:axId val="92900352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437868416"/>
+        <c:axId val="92898432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2667,14 +2690,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437870976"/>
+        <c:crossAx val="92900352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="437870976"/>
+        <c:axId val="92900352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2725,12 +2748,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437868416"/>
+        <c:crossAx val="92898432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="437872896"/>
+        <c:axId val="92906240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2767,12 +2790,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437879168"/>
+        <c:crossAx val="92908160"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="437879168"/>
+        <c:axId val="92908160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2781,7 +2804,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="437872896"/>
+        <c:crossAx val="92906240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3190,7 +3213,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3324,28 +3347,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="R3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="S3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="T3" s="15" t="s">
         <v>16</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -6032,6 +6055,47 @@
         <v>603620.77971210016</v>
       </c>
       <c r="M63" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="12.75">
+      <c r="A64" s="11">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="12">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="12">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="13">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="13">
+        <v>-70500.180121343234</v>
+      </c>
+      <c r="F64" s="14">
+        <v>-63685.799951663794</v>
+      </c>
+      <c r="G64" s="14">
+        <v>1271507.5318450085</v>
+      </c>
+      <c r="H64" s="14">
+        <v>1407558.8292641959</v>
+      </c>
+      <c r="I64" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J64" s="14">
+        <v>2081679.7890976393</v>
+      </c>
+      <c r="K64" s="14">
+        <v>732311.62554152729</v>
+      </c>
+      <c r="L64" s="13">
+        <v>674120.9598334434</v>
+      </c>
+      <c r="M64" s="8">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,6 +75,10 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -476,7 +480,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -662,6 +666,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -671,7 +678,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -856,6 +863,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -899,7 +909,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1085,6 +1095,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1094,7 +1107,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1280,6 +1293,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>2081679.7890976393</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2090580.3030172242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1322,7 +1338,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1508,6 +1524,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1517,7 +1536,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1703,6 +1722,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>732311.62554152729</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>741212.13946111221</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1724,11 +1746,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92879104"/>
-        <c:axId val="92880896"/>
+        <c:axId val="102510592"/>
+        <c:axId val="102512512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92879104"/>
+        <c:axId val="102510592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1771,14 +1793,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92880896"/>
+        <c:crossAx val="102512512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92880896"/>
+        <c:axId val="102512512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1829,7 +1851,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92879104"/>
+        <c:crossAx val="102510592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2020,7 +2042,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2206,6 +2228,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-70500.180121343234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-69892.34544564558</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2220,8 +2245,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="92908160"/>
-        <c:axId val="92906240"/>
+        <c:axId val="102560512"/>
+        <c:axId val="102554240"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2246,7 +2271,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2432,6 +2457,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2441,7 +2469,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2627,6 +2655,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2643,11 +2674,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92898432"/>
-        <c:axId val="92900352"/>
+        <c:axId val="102525952"/>
+        <c:axId val="102552320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92898432"/>
+        <c:axId val="102525952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2690,14 +2721,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92900352"/>
+        <c:crossAx val="102552320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92900352"/>
+        <c:axId val="102552320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2748,12 +2779,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92898432"/>
+        <c:crossAx val="102525952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="92906240"/>
+        <c:axId val="102554240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2790,12 +2821,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92908160"/>
+        <c:crossAx val="102560512"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="92908160"/>
+        <c:axId val="102560512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2804,7 +2835,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="92906240"/>
+        <c:crossAx val="102554240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3213,7 +3244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3347,28 +3378,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -6096,6 +6127,47 @@
         <v>674120.9598334434</v>
       </c>
       <c r="M64" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="12.75">
+      <c r="A65" s="11">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="12">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="12">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="13">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="13">
+        <v>-69892.34544564558</v>
+      </c>
+      <c r="F65" s="14">
+        <v>-62739.989029760065</v>
+      </c>
+      <c r="G65" s="14">
+        <v>1208767.5428152485</v>
+      </c>
+      <c r="H65" s="14">
+        <v>1346566.997738135</v>
+      </c>
+      <c r="I65" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J65" s="14">
+        <v>2090580.3030172242</v>
+      </c>
+      <c r="K65" s="14">
+        <v>741212.13946111221</v>
+      </c>
+      <c r="L65" s="13">
+        <v>744013.30527908902</v>
+      </c>
+      <c r="M65" s="8">
         <v>1</v>
       </c>
     </row>
